--- a/02table/TableS6_anthocyanin_ligin_Bx_in_M19.xlsx
+++ b/02table/TableS6_anthocyanin_ligin_Bx_in_M19.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B8CCDA-2850-A545-8554-53B3327B5CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7110E9B3-28EE-804F-9549-8CDF7A8EDB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35300" yWindow="160" windowWidth="30240" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,7 +366,7 @@
     <t>omt1;Caffeoyl-CoA O-methyltransferase1</t>
   </si>
   <si>
-    <t>Table S6 Genes involved in the anthocyanin, lignin, and benzoxazinoid pathways in module 19.</t>
+    <t>Table S6. Genes involved in the anthocyanin, lignin, and benzoxazinoid pathways in module 19.</t>
   </si>
 </sst>
 </file>
